--- a/premise/data/additional_inventories/lci-synfuels-from-FT-from-natural-gas.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT-from-natural-gas.xlsx
@@ -1433,8 +1433,12 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
-        <v>29</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 40.2 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 21%.</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1556,7 +1560,7 @@
         <v>27</v>
       </c>
       <c r="B17" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C17" t="s">
         <v>24</v>
@@ -1664,8 +1668,12 @@
       <c r="A27" t="s">
         <v>9</v>
       </c>
-      <c r="B27" t="s">
-        <v>30</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 45 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 18%.</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1787,7 +1795,7 @@
         <v>27</v>
       </c>
       <c r="B35" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C35" t="s">
         <v>24</v>
@@ -1892,8 +1900,12 @@
       <c r="A45" t="s">
         <v>9</v>
       </c>
-      <c r="B45" t="s">
-        <v>31</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 44.5 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 24%.</t>
+        </is>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -2015,7 +2027,7 @@
         <v>27</v>
       </c>
       <c r="B53" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C53" t="s">
         <v>24</v>
@@ -2120,8 +2132,12 @@
       <c r="A63" t="s">
         <v>9</v>
       </c>
-      <c r="B63" t="s">
-        <v>32</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 43.3 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 37%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
@@ -2241,7 +2257,7 @@
         <v>27</v>
       </c>
       <c r="B71" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C71" t="s">
         <v>24</v>
@@ -2346,8 +2362,12 @@
       <c r="A81" t="s">
         <v>9</v>
       </c>
-      <c r="B81" t="s">
-        <v>88</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from A.E.M. van den Oever, D. Costa, M. Messagie, Prospective life cycle assessment of alternatively fueled heavy-duty trucks, Applied Energy, 2023, https://doi.org/10.1016/j.apenergy.2023.120834. Energy-based allocation between 3 other co-products (diesel, wax and C5-C10 olefins). Allocation key for this co-product: 11%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -2475,7 +2495,7 @@
         <v>27</v>
       </c>
       <c r="B89" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -2742,8 +2762,12 @@
       <c r="A113" t="s">
         <v>9</v>
       </c>
-      <c r="B113" t="s">
-        <v>29</v>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 40.2 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 21%.</t>
+        </is>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
@@ -2865,7 +2889,7 @@
         <v>27</v>
       </c>
       <c r="B121" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C121" t="s">
         <v>24</v>
@@ -2973,8 +2997,12 @@
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="B131" t="s">
-        <v>30</v>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 45 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 18%.</t>
+        </is>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -3096,7 +3124,7 @@
         <v>27</v>
       </c>
       <c r="B139" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C139" t="s">
         <v>24</v>
@@ -3201,8 +3229,12 @@
       <c r="A149" t="s">
         <v>9</v>
       </c>
-      <c r="B149" t="s">
-        <v>31</v>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 44.5 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 24%.</t>
+        </is>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
@@ -3324,7 +3356,7 @@
         <v>27</v>
       </c>
       <c r="B157" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C157" t="s">
         <v>24</v>
@@ -3429,8 +3461,12 @@
       <c r="A167" t="s">
         <v>9</v>
       </c>
-      <c r="B167" t="s">
-        <v>32</v>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 43.3 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 37%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
@@ -3551,7 +3587,7 @@
         <v>27</v>
       </c>
       <c r="B175" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C175" t="s">
         <v>24</v>
@@ -3656,8 +3692,12 @@
       <c r="A185" t="s">
         <v>9</v>
       </c>
-      <c r="B185" t="s">
-        <v>88</v>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from A.E.M. van den Oever, D. Costa, M. Messagie, Prospective life cycle assessment of alternatively fueled heavy-duty trucks, Applied Energy, 2023, https://doi.org/10.1016/j.apenergy.2023.120834. Energy-based allocation between 3 other co-products (diesel, wax and C5-C10 olefins). Allocation key for this co-product: 11%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
@@ -3785,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="B193" s="14">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C193" t="s">
         <v>24</v>
